--- a/data/evaluation/case_benchmark/evidence_cases_v0.1.xlsx
+++ b/data/evaluation/case_benchmark/evidence_cases_v0.1.xlsx
@@ -2772,8 +2772,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
@@ -2831,6 +2847,21 @@
           <t>url</t>
         </is>
       </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>related_evidence_ids</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>evidence_rationale</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>external_source_refs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2888,6 +2919,21 @@
           <t>https://finance.eastmoney.com/a/202407043122188760.html</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRD_001; EU_003; IEA_001; CASE_004; WB_001</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>R1 美国对华电动车关税/欧盟反补贴(EU_003)是出海触发；R3 中美自泰进口整车与电池数据(TRD_001)显示泰国通道；R4 光模块厂泰国产能(CASE_004)提供同去向类比；R3 全球EV格局(IEA_001)；R2 泰国物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>NEWS_001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2945,6 +2991,21 @@
           <t>https://news.yiche.com/hao/wenzhang/100585175/</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRD_001; CASE_004; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>R1 关税与泰国本地化要求为触发；R2 美国自泰进口整车/电池(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>NEWS_002; COMPANY_REPORT_001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3002,6 +3063,21 @@
           <t>https://m.thepaper.cn/newsDetail_forward_20810032</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; SNE_001; WB_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口电池数据(TRD_001)与中国对越中间品出口(TRD_003)共同刻画越南通道；R3 中国电池厂全球份额(SNE_001)；R2 物流绩效(WB_001)；R4 东南亚建厂类比(CASE_007)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>NEWS_003; NEWS_004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3059,6 +3135,21 @@
           <t>https://finance.sina.com.cn/roll/2026-02-06/doc-inhkwssf2073873.shtml</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>R2 美国自马进口电池(TRD_001)+中国对马中间品出口(TRD_003)；R4 马来西亚工厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>NEWS_005</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3116,6 +3207,21 @@
           <t>https://finance.eastmoney.com/a/202407163131488556.html</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_007; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>R2 美国自越进口(TRD_001)+对越中间品出口(TRD_003)；R4 东南亚建厂类比(CASE_007)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>NEWS_006; NEWS_007</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3173,6 +3279,21 @@
           <t>https://www.thepaper.cn/newsDetail_forward_26493905</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TRD_001; CASE_004; EU_003; IEA_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>R1 欧盟反补贴税(EU_003)抬高欧洲出口成本；R2 美国自泰进口(TRD_001)；R4 泰国建厂类比(CASE_004)；R3 全球EV格局(IEA_001)；R2 物流(WB_001)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>NEWS_008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3230,6 +3351,21 @@
           <t>https://finance.sina.com.cn/stock/relnews/cn/2024-04-12/doc-inarqawt9056004.shtml</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>R2 印尼贸易政策审议包含镍下游化政策(WTO_004)；R1 中国对印尼中间品出口(TRD_003)；R3 电池材料格局(SNE_001)；R2 印尼物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>NEWS_009</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3287,6 +3423,21 @@
           <t>https://futures.hexun.com/2024-04-08/212465761.html</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>WTO_004; TRD_003; SNE_001; WB_001</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化与本地化要求(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 行业格局(SNE_001)；R2 物流绩效(WB_001)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NEWS_010; NEWS_011</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3344,6 +3495,21 @@
           <t>https://www.nbd.com.cn/articles/2026-09-22/4589059.html</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>EU_003; EU_001; EU_004; EU_002; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)+CRMA(EU_002)构成匈牙利建厂的合规与准入约束；R3 宁德时代全球份额(SNE_001)与EV格局(IEA_001)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NEWS_012; NEWS_013</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3401,6 +3567,21 @@
           <t>https://finance.eastmoney.com/a/202507023446498365.html</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>WTO_004; TRD_003; SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>R2 印尼镍下游化/本地化(WTO_004)；R1 对印尼中间品出口(TRD_003)；R3 份额与格局(SNE_001,IEA_001)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NEWS_014</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3458,6 +3639,21 @@
           <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>WTO_004; IEA_001; SNE_001; TRD_003; EU_003</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>R2 印尼本地化政策(WTO_004)直接对应'转为全本地生产'的结果；R3 格局(IEA_001,SNE_001)；R1 中间品出口(TRD_003)+欧盟反补贴(EU_003)说明多地区布局动因</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NEWS_015; NEWS_024; NEWS_025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3515,6 +3711,21 @@
           <t>https://caifuhao.eastmoney.com/news/20260225153639217944650</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>R1 美国对东南亚四国光伏反规避终裁(DOC_001)是该案例决策的直接触发；R4 同调查'已规避/未规避'案例(CASE_002,CASE_003)；R2 美国光伏进口数据(TRD_002)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NEWS_016</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3572,6 +3783,21 @@
           <t>https://finance.sina.com.cn/stock/t/2026-05-27/doc-inhzikrs0845798.shtml</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UNCTAD_001; TRD_003; WB_001; IMF_001</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD 投资报告把三星/富士康类外迁作为 FDI 案例(UNCTAD_001)；R1 对越中间品出口(TRD_003)；R2 越南物流绩效(WB_001)；R3 IMF 对水平型 FDI 的举例(IMF_001)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NEWS_017</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3629,6 +3855,21 @@
           <t>https://finance.eastmoney.com/a/202605223746866215.html</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CASE_001; TRD_003; WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>R4 大旺金属'订单转移后回流'案例(CASE_001)是直接类比；R1 对马中间品出口与配套依赖(TRD_003)；R2 物流成本(WB_001)；R3 行业格局(SNE_001)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>COMPANY_FILING_001; NEWS_018</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3686,6 +3927,21 @@
           <t>https://finance.sina.com.cn/tech/roll/2025-07-03/doc-infeerfp4024842.shtml</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UNCTAD_001; WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>R3 UNCTAD_001 直接引用路透'富士康印度 iPhone 出口'报道（同源提示）；R2 印度贸易政策审议与关税(WTO_002,WTO_003)；R4 回流类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NEWS_019; NEWS_020</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3743,6 +3999,21 @@
           <t>https://3w.huanqiu.com/a/de583b/4TE5JD6omnj</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CASE_001; WB_001; TRD_001; KPMG_001</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>R4 行业层面回流的核心类比是 CASE_001（大旺金属，订单外移印度后回流）；R2 物流与配套成本(WB_001)；R1 关税背景(TRD_001)；R3 美国供应链调查(KPMG_001)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>REUTERS_001; NEWS_023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3798,6 +4069,21 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>https://www.caixin.com/2024-10-28/102250409.html</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>EU_003; EU_001; EU_004; CASE_001</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>R1 欧盟对华BEV反补贴(EU_003)+电池法规(EU_001)+外资审查(EU_004)是收缩欧洲布局的直接约束；R4 回流/收缩类比(CASE_001)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NEWS_021; NEWS_022</t>
         </is>
       </c>
     </row>
